--- a/ReportMTO_starter.xlsx
+++ b/ReportMTO_starter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\ReportMTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0755CFD0-AB43-487C-B124-231C8F03B7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4996B73A-6B4F-411C-8546-5AE31E955D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,6 @@
     <sheet name="tbDATA" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -70,9 +69,6 @@
     <t>AI/API_KEY</t>
   </si>
   <si>
-    <t>sk-ЗАМЕНИТЕ_НА_РЕАЛЬНЫЙ_КЛЮЧ</t>
-  </si>
-  <si>
     <t>AI/MODEL</t>
   </si>
   <si>
@@ -119,13 +115,16 @@
   </si>
   <si>
     <t>Не трогайте этот лист руками. Таблица 'tbDATA' появится здесь автоматически после первого Close &amp; Load To → Table запроса «Query - ImportJSON» (см. инструкцию, шаг 4).</t>
+  </si>
+  <si>
+    <t>sk-90bab1079f2f4f96b948c701d691ab8b</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,6 +154,13 @@
       <color rgb="FF808080"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -176,12 +182,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -571,32 +578,32 @@
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
-        <v>13</v>
+      <c r="B3" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
         <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>8</v>
@@ -604,7 +611,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -612,7 +619,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>10</v>
@@ -620,16 +627,17 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
         <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -644,19 +652,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
         <v>24</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>27</v>
-      </c>
-      <c r="E1" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -674,7 +682,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
